--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -703,15 +703,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="35" min="1" max="1"/>
     <col width="108" customWidth="1" style="35" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="36">
       <c r="B2" s="37" t="inlineStr">
         <is>
@@ -726,6 +727,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="36">
       <c r="B5" s="39" t="inlineStr">
         <is>
@@ -768,6 +770,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="39" customHeight="1" s="36">
       <c r="B12" s="41" t="inlineStr">
         <is>
@@ -775,10 +778,38 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -786,7 +817,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1489,9 +1520,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1499,7 +1530,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1524,6 +1555,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="36">
       <c r="A4" s="53" t="inlineStr">
         <is>
@@ -1671,8 +1703,8 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -524,6 +524,118 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Weighted score by solution — and remember the hierarchy level</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Solution selection'!$B$14:$B$33</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Solution selection'!$J$14:$J$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -1523,6 +1635,7 @@
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1555,7 +1668,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="36">
       <c r="A4" s="53" t="inlineStr">
         <is>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -159,7 +159,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -208,6 +208,11 @@
         <bgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -243,7 +248,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -451,6 +456,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1119,35 +1133,35 @@
       </c>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="36">
-      <c r="A14" s="54" t="inlineStr">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>Ticket closed before adjustment posts</t>
         </is>
       </c>
-      <c r="B14" s="54" t="inlineStr">
-        <is>
-          <t>Block Resolved until the posting webhook confirms</t>
-        </is>
-      </c>
-      <c r="C14" s="54" t="n">
+      <c r="B14" s="70" t="inlineStr">
+        <is>
+          <t>Block Resolved until the webhook confirms</t>
+        </is>
+      </c>
+      <c r="C14" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="54" t="n">
+      <c r="D14" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="E14" s="54" t="n">
+      <c r="E14" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="54" t="n">
+      <c r="F14" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="G14" s="54" t="n">
+      <c r="G14" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="54" t="n">
+      <c r="H14" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="54" t="n">
+      <c r="I14" s="70" t="n">
         <v>5</v>
       </c>
       <c r="J14" s="55">
@@ -1158,23 +1172,49 @@
         <f>IF(J14="","",RANK(J14,$J$14:$J$32))</f>
         <v/>
       </c>
-      <c r="L14" s="57" t="inlineStr">
+      <c r="L14" s="71" t="inlineStr">
         <is>
           <t>2 Design it out</t>
         </is>
       </c>
-      <c r="M14" s="57" t="n"/>
+      <c r="M14" s="71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="36">
-      <c r="A15" s="58" t="n"/>
-      <c r="B15" s="58" t="n"/>
-      <c r="C15" s="58" t="n"/>
-      <c r="D15" s="58" t="n"/>
-      <c r="E15" s="58" t="n"/>
-      <c r="F15" s="58" t="n"/>
-      <c r="G15" s="58" t="n"/>
-      <c r="H15" s="58" t="n"/>
-      <c r="I15" s="58" t="n"/>
+      <c r="A15" s="72" t="inlineStr">
+        <is>
+          <t>Contact reason mis-tagged</t>
+        </is>
+      </c>
+      <c r="B15" s="72" t="inlineStr">
+        <is>
+          <t>Cut to 12 codes and predict from first message</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="72" t="n">
+        <v>5</v>
+      </c>
       <c r="J15" s="55">
         <f>IF(COUNT(C15:I15)=0,"",SUMPRODUCT(C15:I15,$C$10:$I$10))</f>
         <v/>
@@ -1183,19 +1223,49 @@
         <f>IF(J15="","",RANK(J15,$J$14:$J$32))</f>
         <v/>
       </c>
-      <c r="L15" s="57" t="n"/>
-      <c r="M15" s="57" t="n"/>
+      <c r="L15" s="71" t="inlineStr">
+        <is>
+          <t>2 Design it out</t>
+        </is>
+      </c>
+      <c r="M15" s="71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="36">
-      <c r="A16" s="58" t="n"/>
-      <c r="B16" s="58" t="n"/>
-      <c r="C16" s="58" t="n"/>
-      <c r="D16" s="58" t="n"/>
-      <c r="E16" s="58" t="n"/>
-      <c r="F16" s="58" t="n"/>
-      <c r="G16" s="58" t="n"/>
-      <c r="H16" s="58" t="n"/>
-      <c r="I16" s="58" t="n"/>
+      <c r="A16" s="72" t="inlineStr">
+        <is>
+          <t>Billing sweep runs once a day</t>
+        </is>
+      </c>
+      <c r="B16" s="72" t="inlineStr">
+        <is>
+          <t>Move to continuous pull with a WIP cap</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="72" t="n">
+        <v>4</v>
+      </c>
       <c r="J16" s="55">
         <f>IF(COUNT(C16:I16)=0,"",SUMPRODUCT(C16:I16,$C$10:$I$10))</f>
         <v/>
@@ -1204,19 +1274,49 @@
         <f>IF(J16="","",RANK(J16,$J$14:$J$32))</f>
         <v/>
       </c>
-      <c r="L16" s="57" t="n"/>
-      <c r="M16" s="57" t="n"/>
+      <c r="L16" s="71" t="inlineStr">
+        <is>
+          <t>3 Mistake-proof it</t>
+        </is>
+      </c>
+      <c r="M16" s="71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="36">
-      <c r="A17" s="58" t="n"/>
-      <c r="B17" s="58" t="n"/>
-      <c r="C17" s="58" t="n"/>
-      <c r="D17" s="58" t="n"/>
-      <c r="E17" s="58" t="n"/>
-      <c r="F17" s="58" t="n"/>
-      <c r="G17" s="58" t="n"/>
-      <c r="H17" s="58" t="n"/>
-      <c r="I17" s="58" t="n"/>
+      <c r="A17" s="72" t="inlineStr">
+        <is>
+          <t>Batch fails silently</t>
+        </is>
+      </c>
+      <c r="B17" s="72" t="inlineStr">
+        <is>
+          <t>Alert on non-zero exit to on-call</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="72" t="n">
+        <v>5</v>
+      </c>
       <c r="J17" s="55">
         <f>IF(COUNT(C17:I17)=0,"",SUMPRODUCT(C17:I17,$C$10:$I$10))</f>
         <v/>
@@ -1225,19 +1325,49 @@
         <f>IF(J17="","",RANK(J17,$J$14:$J$32))</f>
         <v/>
       </c>
-      <c r="L17" s="57" t="n"/>
-      <c r="M17" s="57" t="n"/>
+      <c r="L17" s="71" t="inlineStr">
+        <is>
+          <t>4 Automatic detection</t>
+        </is>
+      </c>
+      <c r="M17" s="71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="36">
-      <c r="A18" s="58" t="n"/>
-      <c r="B18" s="58" t="n"/>
-      <c r="C18" s="58" t="n"/>
-      <c r="D18" s="58" t="n"/>
-      <c r="E18" s="58" t="n"/>
-      <c r="F18" s="58" t="n"/>
-      <c r="G18" s="58" t="n"/>
-      <c r="H18" s="58" t="n"/>
-      <c r="I18" s="58" t="n"/>
+      <c r="A18" s="72" t="inlineStr">
+        <is>
+          <t>Evidence missing at hand-off</t>
+        </is>
+      </c>
+      <c r="B18" s="72" t="inlineStr">
+        <is>
+          <t>Required-fields form before hand-off</t>
+        </is>
+      </c>
+      <c r="C18" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="72" t="n">
+        <v>4</v>
+      </c>
       <c r="J18" s="55">
         <f>IF(COUNT(C18:I18)=0,"",SUMPRODUCT(C18:I18,$C$10:$I$10))</f>
         <v/>
@@ -1246,19 +1376,49 @@
         <f>IF(J18="","",RANK(J18,$J$14:$J$32))</f>
         <v/>
       </c>
-      <c r="L18" s="57" t="n"/>
-      <c r="M18" s="57" t="n"/>
+      <c r="L18" s="71" t="inlineStr">
+        <is>
+          <t>3 Mistake-proof it</t>
+        </is>
+      </c>
+      <c r="M18" s="71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="36">
-      <c r="A19" s="58" t="n"/>
-      <c r="B19" s="58" t="n"/>
-      <c r="C19" s="58" t="n"/>
-      <c r="D19" s="58" t="n"/>
-      <c r="E19" s="58" t="n"/>
-      <c r="F19" s="58" t="n"/>
-      <c r="G19" s="58" t="n"/>
-      <c r="H19" s="58" t="n"/>
-      <c r="I19" s="58" t="n"/>
+      <c r="A19" s="72" t="inlineStr">
+        <is>
+          <t>Contact reason mis-tagged</t>
+        </is>
+      </c>
+      <c r="B19" s="72" t="inlineStr">
+        <is>
+          <t>Retrain agents on the existing code list</t>
+        </is>
+      </c>
+      <c r="C19" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="72" t="n">
+        <v>2</v>
+      </c>
       <c r="J19" s="55">
         <f>IF(COUNT(C19:I19)=0,"",SUMPRODUCT(C19:I19,$C$10:$I$10))</f>
         <v/>
@@ -1267,8 +1427,16 @@
         <f>IF(J19="","",RANK(J19,$J$14:$J$32))</f>
         <v/>
       </c>
-      <c r="L19" s="57" t="n"/>
-      <c r="M19" s="57" t="n"/>
+      <c r="L19" s="71" t="inlineStr">
+        <is>
+          <t>5 Standard work + training</t>
+        </is>
+      </c>
+      <c r="M19" s="71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="36">
       <c r="A20" s="58" t="n"/>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -573,6 +573,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'Solution selection'!$B$14:$B$33</f>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -158,8 +158,12 @@
       <color rgb="FF0000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -213,6 +217,11 @@
         <fgColor rgb="FFECFAEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -248,7 +257,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -466,6 +475,8 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,6 +600,40 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Mean score</v>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Solution selection'!$O$14:$O$33</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -618,6 +663,9 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -628,7 +676,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>14</col>
+      <col>16</col>
       <colOff>0</colOff>
       <row>12</row>
       <rowOff>0</rowOff>
@@ -946,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="35" min="1" max="1"/>
@@ -1132,6 +1180,11 @@
           <t>Selected?</t>
         </is>
       </c>
+      <c r="O13" s="73" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="36">
       <c r="A14" s="70" t="inlineStr">
@@ -1183,6 +1236,10 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="O14" s="74">
+        <f>IF(J14="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="36">
       <c r="A15" s="72" t="inlineStr">
@@ -1234,6 +1291,10 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="O15" s="74">
+        <f>IF(J15="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="36">
       <c r="A16" s="72" t="inlineStr">
@@ -1285,6 +1346,10 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="O16" s="74">
+        <f>IF(J16="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="36">
       <c r="A17" s="72" t="inlineStr">
@@ -1336,6 +1401,10 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="O17" s="74">
+        <f>IF(J17="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="36">
       <c r="A18" s="72" t="inlineStr">
@@ -1387,6 +1456,10 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="O18" s="74">
+        <f>IF(J18="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="36">
       <c r="A19" s="72" t="inlineStr">
@@ -1437,6 +1510,10 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="O19" s="74">
+        <f>IF(J19="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="36">
@@ -1459,6 +1536,10 @@
       </c>
       <c r="L20" s="57" t="n"/>
       <c r="M20" s="57" t="n"/>
+      <c r="O20" s="74">
+        <f>IF(J20="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="36">
       <c r="A21" s="58" t="n"/>
@@ -1480,6 +1561,10 @@
       </c>
       <c r="L21" s="57" t="n"/>
       <c r="M21" s="57" t="n"/>
+      <c r="O21" s="74">
+        <f>IF(J21="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="36">
       <c r="A22" s="58" t="n"/>
@@ -1501,6 +1586,10 @@
       </c>
       <c r="L22" s="57" t="n"/>
       <c r="M22" s="57" t="n"/>
+      <c r="O22" s="74">
+        <f>IF(J22="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="36">
       <c r="A23" s="58" t="n"/>
@@ -1522,6 +1611,10 @@
       </c>
       <c r="L23" s="57" t="n"/>
       <c r="M23" s="57" t="n"/>
+      <c r="O23" s="74">
+        <f>IF(J23="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="36">
       <c r="A24" s="58" t="n"/>
@@ -1543,6 +1636,10 @@
       </c>
       <c r="L24" s="57" t="n"/>
       <c r="M24" s="57" t="n"/>
+      <c r="O24" s="74">
+        <f>IF(J24="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="36">
       <c r="A25" s="58" t="n"/>
@@ -1564,6 +1661,10 @@
       </c>
       <c r="L25" s="57" t="n"/>
       <c r="M25" s="57" t="n"/>
+      <c r="O25" s="74">
+        <f>IF(J25="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="36">
       <c r="A26" s="58" t="n"/>
@@ -1585,6 +1686,10 @@
       </c>
       <c r="L26" s="57" t="n"/>
       <c r="M26" s="57" t="n"/>
+      <c r="O26" s="74">
+        <f>IF(J26="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="36">
       <c r="A27" s="58" t="n"/>
@@ -1606,6 +1711,10 @@
       </c>
       <c r="L27" s="57" t="n"/>
       <c r="M27" s="57" t="n"/>
+      <c r="O27" s="74">
+        <f>IF(J27="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="36">
       <c r="A28" s="58" t="n"/>
@@ -1627,6 +1736,10 @@
       </c>
       <c r="L28" s="57" t="n"/>
       <c r="M28" s="57" t="n"/>
+      <c r="O28" s="74">
+        <f>IF(J28="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="36">
       <c r="A29" s="58" t="n"/>
@@ -1648,6 +1761,10 @@
       </c>
       <c r="L29" s="57" t="n"/>
       <c r="M29" s="57" t="n"/>
+      <c r="O29" s="74">
+        <f>IF(J29="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="36">
       <c r="A30" s="58" t="n"/>
@@ -1669,6 +1786,10 @@
       </c>
       <c r="L30" s="57" t="n"/>
       <c r="M30" s="57" t="n"/>
+      <c r="O30" s="74">
+        <f>IF(J30="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="36">
       <c r="A31" s="58" t="n"/>
@@ -1690,6 +1811,10 @@
       </c>
       <c r="L31" s="57" t="n"/>
       <c r="M31" s="57" t="n"/>
+      <c r="O31" s="74">
+        <f>IF(J31="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="36">
       <c r="A32" s="58" t="n"/>
@@ -1711,6 +1836,16 @@
       </c>
       <c r="L32" s="57" t="n"/>
       <c r="M32" s="57" t="n"/>
+      <c r="O32" s="74">
+        <f>IF(J32="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="O33" s="74">
+        <f>IF(J33="","",AVERAGE($J$14:$J$33))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="36">
       <c r="A34" s="44" t="inlineStr">

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -162,6 +162,11 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -257,7 +262,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -477,6 +482,10 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="20" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,7 +572,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Weighted score by solution — and remember the hierarchy level</a:t>
+              <a:t>Weighted score by solution — ranked, best first</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -587,12 +596,12 @@
           <invertIfNegative val="0"/>
           <cat>
             <numRef>
-              <f>'Solution selection'!$B$14:$B$33</f>
+              <f>'Solution selection'!$Q$14:$Q$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Solution selection'!$J$14:$J$33</f>
+              <f>'Solution selection'!$R$14:$R$33</f>
             </numRef>
           </val>
         </ser>
@@ -626,7 +635,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Solution selection'!$O$14:$O$33</f>
+              <f>'Solution selection'!$S$14:$S$33</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -676,7 +685,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>16</col>
+      <col>20</col>
       <colOff>0</colOff>
       <row>12</row>
       <rowOff>0</rowOff>
@@ -994,7 +1003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="35" min="1" max="1"/>
@@ -1180,7 +1189,27 @@
           <t>Selected?</t>
         </is>
       </c>
-      <c r="O13" s="73" t="inlineStr">
+      <c r="O13" s="75" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="P13" s="73" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="Q13" s="73" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="R13" s="73" t="inlineStr">
+        <is>
+          <t>Weighted score</t>
+        </is>
+      </c>
+      <c r="S13" s="73" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -1236,8 +1265,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O14" s="74">
-        <f>IF(J14="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O14" s="76">
+        <f>IF(J14="","",RANK(J14,$J$14:$J$33,0)+COUNTIF($J$14:J14,J14)-1)</f>
+        <v/>
+      </c>
+      <c r="P14" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P14,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R14" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P14,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S14" s="74">
+        <f>IF(R14="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1291,8 +1335,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O15" s="74">
-        <f>IF(J15="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O15" s="76">
+        <f>IF(J15="","",RANK(J15,$J$14:$J$33,0)+COUNTIF($J$14:J15,J15)-1)</f>
+        <v/>
+      </c>
+      <c r="P15" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P15,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R15" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P15,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S15" s="74">
+        <f>IF(R15="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1346,8 +1405,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O16" s="74">
-        <f>IF(J16="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O16" s="76">
+        <f>IF(J16="","",RANK(J16,$J$14:$J$33,0)+COUNTIF($J$14:J16,J16)-1)</f>
+        <v/>
+      </c>
+      <c r="P16" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P16,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R16" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P16,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S16" s="74">
+        <f>IF(R16="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1401,8 +1475,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O17" s="74">
-        <f>IF(J17="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O17" s="76">
+        <f>IF(J17="","",RANK(J17,$J$14:$J$33,0)+COUNTIF($J$14:J17,J17)-1)</f>
+        <v/>
+      </c>
+      <c r="P17" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P17,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R17" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P17,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S17" s="74">
+        <f>IF(R17="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1456,8 +1545,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O18" s="74">
-        <f>IF(J18="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O18" s="76">
+        <f>IF(J18="","",RANK(J18,$J$14:$J$33,0)+COUNTIF($J$14:J18,J18)-1)</f>
+        <v/>
+      </c>
+      <c r="P18" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P18,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R18" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P18,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S18" s="74">
+        <f>IF(R18="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1511,8 +1615,23 @@
           <t>No</t>
         </is>
       </c>
-      <c r="O19" s="74">
-        <f>IF(J19="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O19" s="76">
+        <f>IF(J19="","",RANK(J19,$J$14:$J$33,0)+COUNTIF($J$14:J19,J19)-1)</f>
+        <v/>
+      </c>
+      <c r="P19" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P19,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R19" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P19,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S19" s="74">
+        <f>IF(R19="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1536,8 +1655,23 @@
       </c>
       <c r="L20" s="57" t="n"/>
       <c r="M20" s="57" t="n"/>
-      <c r="O20" s="74">
-        <f>IF(J20="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O20" s="76">
+        <f>IF(J20="","",RANK(J20,$J$14:$J$33,0)+COUNTIF($J$14:J20,J20)-1)</f>
+        <v/>
+      </c>
+      <c r="P20" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q20" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P20,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R20" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P20,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S20" s="74">
+        <f>IF(R20="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1561,8 +1695,23 @@
       </c>
       <c r="L21" s="57" t="n"/>
       <c r="M21" s="57" t="n"/>
-      <c r="O21" s="74">
-        <f>IF(J21="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O21" s="76">
+        <f>IF(J21="","",RANK(J21,$J$14:$J$33,0)+COUNTIF($J$14:J21,J21)-1)</f>
+        <v/>
+      </c>
+      <c r="P21" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P21,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R21" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P21,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S21" s="74">
+        <f>IF(R21="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1586,8 +1735,23 @@
       </c>
       <c r="L22" s="57" t="n"/>
       <c r="M22" s="57" t="n"/>
-      <c r="O22" s="74">
-        <f>IF(J22="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O22" s="76">
+        <f>IF(J22="","",RANK(J22,$J$14:$J$33,0)+COUNTIF($J$14:J22,J22)-1)</f>
+        <v/>
+      </c>
+      <c r="P22" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P22,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R22" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P22,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S22" s="74">
+        <f>IF(R22="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1611,8 +1775,23 @@
       </c>
       <c r="L23" s="57" t="n"/>
       <c r="M23" s="57" t="n"/>
-      <c r="O23" s="74">
-        <f>IF(J23="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O23" s="76">
+        <f>IF(J23="","",RANK(J23,$J$14:$J$33,0)+COUNTIF($J$14:J23,J23)-1)</f>
+        <v/>
+      </c>
+      <c r="P23" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P23,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R23" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P23,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S23" s="74">
+        <f>IF(R23="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1636,8 +1815,23 @@
       </c>
       <c r="L24" s="57" t="n"/>
       <c r="M24" s="57" t="n"/>
-      <c r="O24" s="74">
-        <f>IF(J24="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O24" s="76">
+        <f>IF(J24="","",RANK(J24,$J$14:$J$33,0)+COUNTIF($J$14:J24,J24)-1)</f>
+        <v/>
+      </c>
+      <c r="P24" s="77" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q24" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P24,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R24" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P24,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S24" s="74">
+        <f>IF(R24="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1661,8 +1855,23 @@
       </c>
       <c r="L25" s="57" t="n"/>
       <c r="M25" s="57" t="n"/>
-      <c r="O25" s="74">
-        <f>IF(J25="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O25" s="76">
+        <f>IF(J25="","",RANK(J25,$J$14:$J$33,0)+COUNTIF($J$14:J25,J25)-1)</f>
+        <v/>
+      </c>
+      <c r="P25" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q25" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P25,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R25" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P25,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S25" s="74">
+        <f>IF(R25="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1686,8 +1895,23 @@
       </c>
       <c r="L26" s="57" t="n"/>
       <c r="M26" s="57" t="n"/>
-      <c r="O26" s="74">
-        <f>IF(J26="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O26" s="76">
+        <f>IF(J26="","",RANK(J26,$J$14:$J$33,0)+COUNTIF($J$14:J26,J26)-1)</f>
+        <v/>
+      </c>
+      <c r="P26" s="77" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q26" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P26,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R26" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P26,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S26" s="74">
+        <f>IF(R26="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1711,8 +1935,23 @@
       </c>
       <c r="L27" s="57" t="n"/>
       <c r="M27" s="57" t="n"/>
-      <c r="O27" s="74">
-        <f>IF(J27="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O27" s="76">
+        <f>IF(J27="","",RANK(J27,$J$14:$J$33,0)+COUNTIF($J$14:J27,J27)-1)</f>
+        <v/>
+      </c>
+      <c r="P27" s="77" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q27" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P27,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R27" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P27,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S27" s="74">
+        <f>IF(R27="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1736,8 +1975,23 @@
       </c>
       <c r="L28" s="57" t="n"/>
       <c r="M28" s="57" t="n"/>
-      <c r="O28" s="74">
-        <f>IF(J28="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O28" s="76">
+        <f>IF(J28="","",RANK(J28,$J$14:$J$33,0)+COUNTIF($J$14:J28,J28)-1)</f>
+        <v/>
+      </c>
+      <c r="P28" s="77" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q28" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P28,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R28" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P28,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S28" s="74">
+        <f>IF(R28="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1761,8 +2015,23 @@
       </c>
       <c r="L29" s="57" t="n"/>
       <c r="M29" s="57" t="n"/>
-      <c r="O29" s="74">
-        <f>IF(J29="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O29" s="76">
+        <f>IF(J29="","",RANK(J29,$J$14:$J$33,0)+COUNTIF($J$14:J29,J29)-1)</f>
+        <v/>
+      </c>
+      <c r="P29" s="77" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q29" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P29,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R29" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P29,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S29" s="74">
+        <f>IF(R29="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1786,8 +2055,23 @@
       </c>
       <c r="L30" s="57" t="n"/>
       <c r="M30" s="57" t="n"/>
-      <c r="O30" s="74">
-        <f>IF(J30="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O30" s="76">
+        <f>IF(J30="","",RANK(J30,$J$14:$J$33,0)+COUNTIF($J$14:J30,J30)-1)</f>
+        <v/>
+      </c>
+      <c r="P30" s="77" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q30" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P30,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R30" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P30,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S30" s="74">
+        <f>IF(R30="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1811,8 +2095,23 @@
       </c>
       <c r="L31" s="57" t="n"/>
       <c r="M31" s="57" t="n"/>
-      <c r="O31" s="74">
-        <f>IF(J31="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O31" s="76">
+        <f>IF(J31="","",RANK(J31,$J$14:$J$33,0)+COUNTIF($J$14:J31,J31)-1)</f>
+        <v/>
+      </c>
+      <c r="P31" s="77" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q31" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P31,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R31" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P31,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S31" s="74">
+        <f>IF(R31="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
@@ -1836,14 +2135,44 @@
       </c>
       <c r="L32" s="57" t="n"/>
       <c r="M32" s="57" t="n"/>
-      <c r="O32" s="74">
-        <f>IF(J32="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O32" s="76">
+        <f>IF(J32="","",RANK(J32,$J$14:$J$33,0)+COUNTIF($J$14:J32,J32)-1)</f>
+        <v/>
+      </c>
+      <c r="P32" s="77" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q32" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P32,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R32" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P32,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S32" s="74">
+        <f>IF(R32="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="O33" s="74">
-        <f>IF(J33="","",AVERAGE($J$14:$J$33))</f>
+      <c r="O33" s="76">
+        <f>IF(J33="","",RANK(J33,$J$14:$J$33,0)+COUNTIF($J$14:J33,J33)-1)</f>
+        <v/>
+      </c>
+      <c r="P33" s="77" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q33" s="78">
+        <f>IFERROR(INDEX($B$14:$B$33,MATCH(P33,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="R33" s="74">
+        <f>IFERROR(INDEX($J$14:$J$33,MATCH(P33,$O$14:$O$33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="S33" s="74">
+        <f>IF(R33="","",AVERAGE($R$14:$R$33))</f>
         <v/>
       </c>
     </row>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -585,6 +585,9 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <v>Weighted score</v>
+          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="1F4E79"/>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -572,7 +572,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Weighted score by solution — ranked, best first</a:t>
+              <a:t>Weighted score by solution — the top three are the shortlist</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -589,22 +589,129 @@
             <v>Weighted score</v>
           </tx>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1F4E79"/>
-            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Solution selection'!$Q$14:$Q$33</f>
+              <f>'Solution selection'!$Q$14:$Q$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Solution selection'!$R$14:$R$33</f>
+              <f>'Solution selection'!$R$14:$R$23</f>
             </numRef>
           </val>
         </ser>
@@ -612,44 +719,10 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <v>Mean score</v>
-          </tx>
-          <spPr>
-            <a:ln w="18000">
-              <a:solidFill>
-                <a:srgbClr val="C0392B"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <val>
-            <numRef>
-              <f>'Solution selection'!$S$14:$S$33</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="minMax"/>
+          <orientation val="maxMin"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -658,8 +731,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -675,9 +748,6 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -693,7 +763,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6120000" cy="3960000"/>
+    <ext cx="6120000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1212,11 +1282,7 @@
           <t>Weighted score</t>
         </is>
       </c>
-      <c r="S13" s="73" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
+      <c r="S13" s="73" t="n"/>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="36">
       <c r="A14" s="70" t="inlineStr">
@@ -1283,10 +1349,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P14,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S14" s="74">
-        <f>IF(R14="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S14" s="74" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1" s="36">
       <c r="A15" s="72" t="inlineStr">
@@ -1353,10 +1416,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P15,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S15" s="74">
-        <f>IF(R15="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S15" s="74" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1" s="36">
       <c r="A16" s="72" t="inlineStr">
@@ -1423,10 +1483,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P16,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S16" s="74">
-        <f>IF(R16="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S16" s="74" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1" s="36">
       <c r="A17" s="72" t="inlineStr">
@@ -1493,10 +1550,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P17,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S17" s="74">
-        <f>IF(R17="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S17" s="74" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1" s="36">
       <c r="A18" s="72" t="inlineStr">
@@ -1563,10 +1617,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P18,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S18" s="74">
-        <f>IF(R18="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S18" s="74" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1" s="36">
       <c r="A19" s="72" t="inlineStr">
@@ -1633,10 +1684,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P19,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S19" s="74">
-        <f>IF(R19="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S19" s="74" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1" s="36">
       <c r="A20" s="58" t="n"/>
@@ -1673,10 +1721,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P20,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S20" s="74">
-        <f>IF(R20="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S20" s="74" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1" s="36">
       <c r="A21" s="58" t="n"/>
@@ -1713,10 +1758,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P21,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S21" s="74">
-        <f>IF(R21="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S21" s="74" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1" s="36">
       <c r="A22" s="58" t="n"/>
@@ -1753,10 +1795,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P22,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S22" s="74">
-        <f>IF(R22="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S22" s="74" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1" s="36">
       <c r="A23" s="58" t="n"/>
@@ -1793,10 +1832,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P23,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S23" s="74">
-        <f>IF(R23="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S23" s="74" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1" s="36">
       <c r="A24" s="58" t="n"/>
@@ -1833,10 +1869,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P24,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S24" s="74">
-        <f>IF(R24="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S24" s="74" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1" s="36">
       <c r="A25" s="58" t="n"/>
@@ -1873,10 +1906,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P25,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S25" s="74">
-        <f>IF(R25="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S25" s="74" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1" s="36">
       <c r="A26" s="58" t="n"/>
@@ -1913,10 +1943,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P26,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S26" s="74">
-        <f>IF(R26="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S26" s="74" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1" s="36">
       <c r="A27" s="58" t="n"/>
@@ -1953,10 +1980,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P27,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S27" s="74">
-        <f>IF(R27="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S27" s="74" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1" s="36">
       <c r="A28" s="58" t="n"/>
@@ -1993,10 +2017,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P28,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S28" s="74">
-        <f>IF(R28="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S28" s="74" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1" s="36">
       <c r="A29" s="58" t="n"/>
@@ -2033,10 +2054,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P29,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S29" s="74">
-        <f>IF(R29="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S29" s="74" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1" s="36">
       <c r="A30" s="58" t="n"/>
@@ -2073,10 +2091,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P30,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S30" s="74">
-        <f>IF(R30="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S30" s="74" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1" s="36">
       <c r="A31" s="58" t="n"/>
@@ -2113,10 +2128,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P31,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S31" s="74">
-        <f>IF(R31="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S31" s="74" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1" s="36">
       <c r="A32" s="58" t="n"/>
@@ -2153,10 +2165,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P32,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S32" s="74">
-        <f>IF(R32="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S32" s="74" t="n"/>
     </row>
     <row r="33">
       <c r="O33" s="76">
@@ -2174,10 +2183,7 @@
         <f>IFERROR(INDEX($J$14:$J$33,MATCH(P33,$O$14:$O$33,0)),"")</f>
         <v/>
       </c>
-      <c r="S33" s="74">
-        <f>IF(R33="","",AVERAGE($R$14:$R$33))</f>
-        <v/>
-      </c>
+      <c r="S33" s="74" t="n"/>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="36">
       <c r="A34" s="44" t="inlineStr">

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -758,9 +758,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>20</col>
+      <col>19</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="3240000"/>
@@ -1102,6 +1102,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="36">
       <c r="A4" s="44" t="inlineStr">
         <is>
@@ -1145,6 +1146,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="19.5" customHeight="1" s="36">
       <c r="A9" s="44" t="inlineStr">
         <is>
@@ -1189,6 +1191,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="19.5" customHeight="1" s="36">
       <c r="A12" s="44" t="inlineStr">
         <is>
@@ -2236,6 +2239,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="39" customHeight="1" s="36">
       <c r="A40" s="60" t="inlineStr">
         <is>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -2314,6 +2314,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="36">
       <c r="A4" s="53" t="inlineStr">
         <is>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -262,7 +262,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -486,6 +486,15 @@
     <xf numFmtId="1" fontId="20" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2398,20 +2407,20 @@
       </c>
     </row>
     <row r="8" ht="25.5" customHeight="1" s="36">
-      <c r="A8" s="64" t="n">
+      <c r="A8" s="79" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="65" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>Detect it</t>
         </is>
       </c>
-      <c r="C8" s="66" t="inlineStr">
+      <c r="C8" s="81" t="inlineStr">
         <is>
           <t>The system flags the error the moment it happens.</t>
         </is>
       </c>
-      <c r="D8" s="65" t="inlineStr">
+      <c r="D8" s="80" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -168,7 +168,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -227,6 +227,11 @@
         <fgColor rgb="FFF2F7FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9E3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -262,7 +267,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -493,6 +498,15 @@
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2407,20 +2421,20 @@
       </c>
     </row>
     <row r="8" ht="25.5" customHeight="1" s="36">
-      <c r="A8" s="79" t="n">
+      <c r="A8" s="82" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="80" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
         <is>
           <t>Detect it</t>
         </is>
       </c>
-      <c r="C8" s="81" t="inlineStr">
+      <c r="C8" s="84" t="inlineStr">
         <is>
           <t>The system flags the error the moment it happens.</t>
         </is>
       </c>
-      <c r="D8" s="80" t="inlineStr">
+      <c r="D8" s="83" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -167,6 +167,24 @@
       <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1D6F42"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFB45309"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFB91C1C"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -267,7 +285,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -507,6 +525,18 @@
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2361,120 +2391,120 @@
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" s="36">
-      <c r="A5" s="61" t="n">
+      <c r="A5" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="62" t="inlineStr">
+      <c r="B5" s="86" t="inlineStr">
         <is>
           <t>Eliminate the demand</t>
         </is>
       </c>
-      <c r="C5" s="63" t="inlineStr">
+      <c r="C5" s="86" t="inlineStr">
         <is>
           <t>Fix the upstream cause so the contact never happens at all.</t>
         </is>
       </c>
-      <c r="D5" s="62" t="inlineStr">
+      <c r="D5" s="86" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" s="36">
-      <c r="A6" s="61" t="n">
+      <c r="A6" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="62" t="inlineStr">
+      <c r="B6" s="86" t="inlineStr">
         <is>
           <t>Design it out</t>
         </is>
       </c>
-      <c r="C6" s="63" t="inlineStr">
+      <c r="C6" s="86" t="inlineStr">
         <is>
           <t>Change the system so the error is impossible.</t>
         </is>
       </c>
-      <c r="D6" s="62" t="inlineStr">
+      <c r="D6" s="86" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25.5" customHeight="1" s="36">
-      <c r="A7" s="61" t="n">
+      <c r="A7" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="62" t="inlineStr">
+      <c r="B7" s="86" t="inlineStr">
         <is>
           <t>Guide it</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="86" t="inlineStr">
         <is>
           <t>The workflow forces the right path; doing it wrong needs a deliberate override.</t>
         </is>
       </c>
-      <c r="D7" s="62" t="inlineStr">
+      <c r="D7" s="86" t="inlineStr">
         <is>
           <t>Very durable</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25.5" customHeight="1" s="36">
-      <c r="A8" s="82" t="n">
+      <c r="A8" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="87" t="inlineStr">
         <is>
           <t>Detect it</t>
         </is>
       </c>
-      <c r="C8" s="84" t="inlineStr">
+      <c r="C8" s="87" t="inlineStr">
         <is>
           <t>The system flags the error the moment it happens.</t>
         </is>
       </c>
-      <c r="D8" s="83" t="inlineStr">
+      <c r="D8" s="87" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" s="36">
-      <c r="A9" s="67" t="n">
+      <c r="A9" s="85" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="68" t="inlineStr">
+      <c r="B9" s="88" t="inlineStr">
         <is>
           <t>Standardise it</t>
         </is>
       </c>
-      <c r="C9" s="69" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>Documented standard work with a visible reference.</t>
         </is>
       </c>
-      <c r="D9" s="68" t="inlineStr">
+      <c r="D9" s="88" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1" s="36">
-      <c r="A10" s="67" t="n">
+      <c r="A10" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="68" t="inlineStr">
+      <c r="B10" s="88" t="inlineStr">
         <is>
           <t>Train and remind</t>
         </is>
       </c>
-      <c r="C10" s="69" t="inlineStr">
+      <c r="C10" s="88" t="inlineStr">
         <is>
           <t>Coaching, comms, reminders, posters.</t>
         </is>
       </c>
-      <c r="D10" s="68" t="inlineStr">
+      <c r="D10" s="88" t="inlineStr">
         <is>
           <t>Six to ten weeks</t>
         </is>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -285,7 +285,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -538,6 +538,15 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1190,12 +1199,12 @@
     <row r="7" ht="15" customHeight="1" s="36">
       <c r="A7" s="48" t="inlineStr">
         <is>
-          <t>Row 1 example</t>
+          <t>Green cells</t>
         </is>
       </c>
       <c r="B7" s="46" t="inlineStr">
         <is>
-          <t>A realistic worked example, so you can see the expected format. Delete or overwrite it.</t>
+          <t>A realistic worked example, so you can see the expected format and the sheet is not blank when you open it. Replace it with your own.</t>
         </is>
       </c>
     </row>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -285,7 +285,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -547,6 +547,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1254,10 +1257,10 @@
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="19.5" customHeight="1" s="36">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>SCORE EACH OPTION 1–5 ON EVERY CRITERION.  Generate at least three options per root cause before you score.</t>
+    <row r="12" ht="144" customHeight="1" s="36">
+      <c r="A12" s="92" t="inlineStr">
+        <is>
+          <t>SCORE EACH OPTION 1–5 ON EVERY CRITERION.  Generate at least three options per root cause before you score.  ·  Key: Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk' · Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15) · Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt · Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
         </is>
       </c>
     </row>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -1257,10 +1257,18 @@
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="144" customHeight="1" s="36">
+    <row r="12" ht="312" customHeight="1" s="36">
       <c r="A12" s="92" t="inlineStr">
         <is>
-          <t>SCORE EACH OPTION 1–5 ON EVERY CRITERION.  Generate at least three options per root cause before you score.  ·  Key: Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk' · Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15) · Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt · Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+          <t>SCORE EACH OPTION 1–5 ON EVERY CRITERION.  Generate at least three options per root cause before you score.  ·  Key:
+• Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
+• Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt
+• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
+• Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
+• Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt
+• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
         </is>
       </c>
     </row>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -185,6 +185,11 @@
       <color rgb="FFB91C1C"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -285,7 +290,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -550,6 +555,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -823,7 +831,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>22</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -1141,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="35" min="1" max="1"/>
@@ -1151,6 +1159,15 @@
     <col width="7" customWidth="1" style="35" min="11" max="11"/>
     <col width="17" customWidth="1" style="35" min="12" max="12"/>
     <col width="11" customWidth="1" style="35" min="13" max="13"/>
+    <col width="13" customWidth="1" style="36" min="21" max="21"/>
+    <col width="13" customWidth="1" style="36" min="22" max="22"/>
+    <col width="13" customWidth="1" style="36" min="23" max="23"/>
+    <col width="13" customWidth="1" style="36" min="24" max="24"/>
+    <col width="13" customWidth="1" style="36" min="25" max="25"/>
+    <col width="13" customWidth="1" style="36" min="26" max="26"/>
+    <col width="13" customWidth="1" style="36" min="27" max="27"/>
+    <col width="13" customWidth="1" style="36" min="28" max="28"/>
+    <col width="13" customWidth="1" style="36" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="36">
@@ -1257,10 +1274,18 @@
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="312" customHeight="1" s="36">
+    <row r="12" ht="600" customHeight="1" s="36">
       <c r="A12" s="92" t="inlineStr">
         <is>
           <t>SCORE EACH OPTION 1–5 ON EVERY CRITERION.  Generate at least three options per root cause before you score.  ·  Key:
+• Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
+• Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt
+• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
+• Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
+• Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt
+• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
 • Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
 • Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt
@@ -2243,7 +2268,7 @@
       </c>
       <c r="S32" s="74" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="77" customHeight="1" s="36">
       <c r="O33" s="76">
         <f>IF(J33="","",RANK(J33,$J$14:$J$33,0)+COUNTIF($J$14:J33,J33)-1)</f>
         <v/>
@@ -2260,6 +2285,12 @@
         <v/>
       </c>
       <c r="S33" s="74" t="n"/>
+      <c r="U33" s="93" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Scores land back on the 1-5 scale because the weights sum to 1. A shortlist, not a decision: check the countermeasure level of the top few before you commit, because a high-scoring solution that only guides behaviour will decay while a lower-scoring one that designs the failure out will not.
+SO:  Take the shortlist to the countermeasure hierarchy before choosing. Prefer a slightly lower-scoring solution that designs the failure out over a higher-scoring one that asks people to remember — the second decays within two quarters.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="36">
       <c r="A34" s="44" t="inlineStr">
@@ -2321,7 +2352,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A1:M1"/>
@@ -2333,6 +2364,7 @@
     <mergeCell ref="A12:M12"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="A40:M40"/>
+    <mergeCell ref="U33:AC33"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A36:D36"/>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -1274,22 +1274,10 @@
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="600" customHeight="1" s="36">
+    <row r="12" ht="168" customHeight="1" s="36">
       <c r="A12" s="92" t="inlineStr">
         <is>
           <t>SCORE EACH OPTION 1–5 ON EVERY CRITERION.  Generate at least three options per root cause before you score.  ·  Key:
-• Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
-• Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt
-• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
-• Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
-• Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt
-• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
-• Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
-• Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt
-• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
 • Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
 • Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -290,7 +290,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -557,6 +557,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1110,11 +1113,41 @@
     </row>
     <row r="13"/>
     <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
+    <row r="15" ht="26" customHeight="1" s="36">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39" customHeight="1" s="36">
+      <c r="A16" s="93" t="inlineStr">
+        <is>
+          <t>Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1" s="36">
+      <c r="A17" s="93" t="inlineStr">
+        <is>
+          <t>Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1" s="36">
+      <c r="A18" s="93" t="inlineStr">
+        <is>
+          <t>Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39" customHeight="1" s="36">
+      <c r="A19" s="93" t="inlineStr">
+        <is>
+          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+        </is>
+      </c>
+    </row>
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
@@ -1137,6 +1170,13 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+  </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1274,14 +1314,14 @@
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="168" customHeight="1" s="36">
+    <row r="12" ht="108" customHeight="1" s="36">
       <c r="A12" s="92" t="inlineStr">
         <is>
           <t>SCORE EACH OPTION 1–5 ON EVERY CRITERION.  Generate at least three options per root cause before you score.  ·  Key:
-• Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects. A criterion phrased as a negative would invert the arithmetic against its neighbours, which is why it is written as 'low risk' rather than 'risk'
-• Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale. The weights here run 0.25, 0.20, 0.15 and four at 0.10 (C10:I10) and must sum to 1, or the scores are not comparable. The deferred-close option scores 4.30 against 3.60 for the next one (J14, J15)
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt
-• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+• Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects.
+• Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale.
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place.
+• Rank = position by weighted total, 1 being highest.</t>
         </is>
       </c>
     </row>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -1043,6 +1043,12 @@
   <cols>
     <col width="3" customWidth="1" style="35" min="1" max="1"/>
     <col width="108" customWidth="1" style="35" min="2" max="2"/>
+    <col width="13" customWidth="1" style="36" min="3" max="3"/>
+    <col width="13" customWidth="1" style="36" min="4" max="4"/>
+    <col width="13" customWidth="1" style="36" min="5" max="5"/>
+    <col width="13" customWidth="1" style="36" min="6" max="6"/>
+    <col width="13" customWidth="1" style="36" min="7" max="7"/>
+    <col width="13" customWidth="1" style="36" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1134,19 +1140,15 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="44" customHeight="1" s="36">
+    <row r="18" ht="22" customHeight="1" s="36">
       <c r="A18" s="93" t="inlineStr">
         <is>
-          <t>Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
+          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
         </is>
       </c>
     </row>
     <row r="19" ht="39" customHeight="1" s="36">
-      <c r="A19" s="93" t="inlineStr">
-        <is>
-          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
-        </is>
-      </c>
+      <c r="A19" s="93" t="n"/>
     </row>
     <row r="20"/>
     <row r="21"/>
@@ -1314,13 +1316,12 @@
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="108" customHeight="1" s="36">
+    <row r="12" ht="84" customHeight="1" s="36">
       <c r="A12" s="92" t="inlineStr">
         <is>
           <t>SCORE EACH OPTION 1–5 ON EVERY CRITERION.  Generate at least three options per root cause before you score.  ·  Key:
 • Low risk of side-effects = 1-5, and the label points the same way as every other column: 5 is GOOD, meaning few side-effects.
 • Weighted score = each criterion's 1-5 score times the weight above it, added up, so it lands back on the 1-5 scale.
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place.
 • Rank = position by weighted total, 1 being highest.</t>
         </is>
       </c>

--- a/templates/15-solution-selection-matrix.xlsx
+++ b/templates/15-solution-selection-matrix.xlsx
@@ -1143,7 +1143,7 @@
     <row r="18" ht="22" customHeight="1" s="36">
       <c r="A18" s="93" t="inlineStr">
         <is>
-          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Always read it with the totals beside it: a rank on its own hides both a photo finish and an exact tie, and no amount of re-scoring separates two rows that scored the same</t>
         </is>
       </c>
     </row>
